--- a/INFRACOES_DB.xlsx
+++ b/INFRACOES_DB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9c248efe7b03c2f/Desktop/APP-VISA/Drogarias/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9c248efe7b03c2f/Desktop/APP_DROGARIAS-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{9CDC3BE8-485D-4911-957E-5AA9D2559CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E584995-B024-4ED8-9291-05666235AF4B}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{9CDC3BE8-485D-4911-957E-5AA9D2559CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0DAC54E-0594-4C3C-815B-CB3D40C6CDE5}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{B8A7E7A7-A36F-4A9B-99FB-2AA9064E12AB}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{B8A7E7A7-A36F-4A9B-99FB-2AA9064E12AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="71">
   <si>
     <t>id_lei_artigo</t>
   </si>
@@ -67,12 +67,6 @@
   </si>
   <si>
     <t>Apresentar AFE (Autorização de Funcionamento da Empresa) emitida pela ANVISA válida e ativa, para as atividades desenvolvidas no local: {lista_atividades_AFE}</t>
-  </si>
-  <si>
-    <t>As farmácias e drogarias devem possuir os seguintes documentos no estabelecimento: Autorização de Funcionamento de Empresa (AFE) expedida pela Anvisa</t>
-  </si>
-  <si>
-    <t>As farmácias e drogarias devem possuir os seguintes documentos no estabelecimento: Certidão de Regularidade Técnica, emitido pelo Conselho Regional de Farmácia da respectiva jurisdição</t>
   </si>
   <si>
     <t>RDC44_2_I</t>
@@ -115,9 +109,6 @@
   </si>
   <si>
     <t>RDC44_12</t>
-  </si>
-  <si>
-    <t>O estabelecimento deve ser abastecido com água potável e, quando possuir caixa d'água própria, ela deve estar devidamente protegida para evitar a entrada de animais de qualquer porte, sujidades ou quaisquer outros contaminantes, devendo definir procedimentos escritos para a limpeza da caixa d'água e manter os registros que comprovem sua realização.</t>
   </si>
   <si>
     <t xml:space="preserve">{AVCB_CLCB} nº {n_AVCB}, emitido em {emissao_AVCB}, válido até {validade_AVCB}. </t>
@@ -168,9 +159,6 @@
     <t>Apresentar Plano de Gerenciamento de Resíduos de Serviços de Saúde (PGRSS) adequado ao funcionamento do estabelecimento.</t>
   </si>
   <si>
-    <t>As farmácias e drogarias devem possuir Plano de Gerenciamento de Resíduos de Serviços de Saúde - PGRSS, conforme legislação específica.</t>
-  </si>
-  <si>
     <t>6_item_II</t>
   </si>
   <si>
@@ -180,17 +168,10 @@
     <t>RDC_222_2018</t>
   </si>
   <si>
-    <t>No PGRSS, o gerador de RSS deve descrever os procedimentos relacionados ao gerenciamento dos RSS quanto à
-geração, à segregação, ao acondicionamento, à identificação, à coleta, ao armazenamento, ao transporte, ao tratamento e à disposição final ambientalmente adequada</t>
-  </si>
-  <si>
     <t>Não apresentou comprovantes válidos de recolhimento de resíduos infectantes e químicos.</t>
   </si>
   <si>
     <t>Apresentar comprovantes válidos de recolhimento de resíduos infectantes e químicos.</t>
-  </si>
-  <si>
-    <t>O estabelecimento deve manter registros, no mínimo, referentes a execução de programa de combate a insetos e roedores</t>
   </si>
   <si>
     <t>88_item_IV</t>
@@ -264,6 +245,12 @@
   </si>
   <si>
     <t xml:space="preserve">Autorização de Funcionamento de Empresa (AFE) emitida pela Agência Nacional de Vigilância Sanitária (ANVISA), sob o número {numero_AFE}  em {data_emissao_AFE} com Status {status_AFE}.  </t>
+  </si>
+  <si>
+    <t>pergunta</t>
+  </si>
+  <si>
+    <t>Há farmacêutico responsável no momento da inspeção?</t>
   </si>
 </sst>
 </file>
@@ -638,15 +625,15 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="107.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B2" s="1">
         <v>3</v>
@@ -655,16 +642,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -785,13 +772,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91B7C6FF-C8B6-41D2-B1B6-217B138148F2}">
-  <dimension ref="A1:G769"/>
+  <dimension ref="A1:G770"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
     <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
@@ -808,258 +795,234 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="123" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="B4" s="1" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="123" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="1">
-        <v>12</v>
+        <v>46</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="1">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="153.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="195" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="138" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="153.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="195" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="138" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="1" t="s">
+    </row>
+    <row r="11" spans="1:7" ht="180" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="B11" s="1">
+        <v>97</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="180" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="12" spans="1:7" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="1">
-        <v>97</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="74.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-    </row>
+    </row>
+    <row r="13" spans="1:7" ht="74.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
@@ -7863,6 +7826,15 @@
       <c r="E769" s="1"/>
       <c r="F769" s="1"/>
       <c r="G769" s="1"/>
+    </row>
+    <row r="770" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A770" s="1"/>
+      <c r="B770" s="1"/>
+      <c r="C770" s="1"/>
+      <c r="D770" s="1"/>
+      <c r="E770" s="1"/>
+      <c r="F770" s="1"/>
+      <c r="G770" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -7900,33 +7872,33 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -7940,25 +7912,25 @@
     </row>
     <row r="4" spans="1:7" ht="165" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -10106,7 +10078,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
